--- a/artfynd/A 23584-2026 artfynd.xlsx
+++ b/artfynd/A 23584-2026 artfynd.xlsx
@@ -1238,7 +1238,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Francis Rogers, Ki Mähler, Annika Leers</t>
+          <t>Annika Leers, Ki Mähler, Francis Rogers</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 23584-2026 artfynd.xlsx
+++ b/artfynd/A 23584-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AY25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2139,10 +2139,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>134944921</v>
+        <v>135188692</v>
       </c>
       <c r="B15" t="n">
-        <v>45268</v>
+        <v>57162</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2150,37 +2150,45 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>102920</v>
+        <v>100138</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grön mosaikslända</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Aeshna viridis</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Eversmann, 1836</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Aspbolet, Upl</t>
+          <t>Aspbolsberget, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>624306</v>
+        <v>624017</v>
       </c>
       <c r="R15" t="n">
-        <v>6637654</v>
+        <v>6637855</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2204,22 +2212,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2246,10 +2254,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>134944923</v>
+        <v>134944921</v>
       </c>
       <c r="B16" t="n">
-        <v>58839</v>
+        <v>45268</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2257,54 +2265,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>208249</v>
+        <v>102920</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Grön mosaikslända</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Aeshna viridis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>Eversmann, 1836</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Aspbolet, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>624283</v>
+        <v>624306</v>
       </c>
       <c r="R16" t="n">
-        <v>6637622</v>
+        <v>6637654</v>
       </c>
       <c r="S16" t="n">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2333,7 +2324,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2343,7 +2334,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2352,7 +2343,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2371,10 +2361,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>134938793</v>
+        <v>134944923</v>
       </c>
       <c r="B17" t="n">
-        <v>100815</v>
+        <v>58839</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2382,41 +2372,54 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219851</v>
+        <v>208249</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Hässlebrodd</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Milium effusum</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Stennässjön öster om, Upl</t>
+          <t>Aspbolet, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>624299</v>
+        <v>624283</v>
       </c>
       <c r="R17" t="n">
-        <v>6637654</v>
+        <v>6637622</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>34</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2445,7 +2448,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2455,7 +2458,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2471,22 +2474,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Ki Mähler</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Ki Mähler</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>134920532</v>
+        <v>134938793</v>
       </c>
       <c r="B18" t="n">
-        <v>108205</v>
+        <v>100815</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2494,51 +2497,41 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220083</v>
+        <v>219851</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Brudborste</t>
+          <t>Hässlebrodd</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cirsium heterophyllum</t>
+          <t>Milium effusum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hill</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Stennässjön öster om, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>624238</v>
+        <v>624299</v>
       </c>
       <c r="R18" t="n">
-        <v>6637712</v>
+        <v>6637654</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2567,7 +2560,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2577,7 +2570,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2586,6 +2579,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2604,10 +2598,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>134921287</v>
+        <v>134920532</v>
       </c>
       <c r="B19" t="n">
-        <v>106141</v>
+        <v>108205</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2615,24 +2609,33 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221101</v>
+        <v>220083</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Springkorn</t>
+          <t>Brudborste</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Impatiens noli-tangere</t>
+          <t>Cirsium heterophyllum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) Hill</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -2644,13 +2647,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>624299</v>
+        <v>624238</v>
       </c>
       <c r="R19" t="n">
-        <v>6637654</v>
+        <v>6637712</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2679,7 +2682,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2689,7 +2692,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2716,10 +2719,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>134859454</v>
+        <v>134921287</v>
       </c>
       <c r="B20" t="n">
-        <v>101403</v>
+        <v>106141</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2727,45 +2730,42 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>222498</v>
+        <v>221101</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Springkorn</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Impatiens noli-tangere</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Aspbolsberget, Upl</t>
+          <t>Stennässjön öster om, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>624157</v>
+        <v>624299</v>
       </c>
       <c r="R20" t="n">
-        <v>6637639</v>
+        <v>6637654</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2789,12 +2789,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2803,26 +2813,25 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Annika Leers</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Annika Leers, Francis Rogers</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>134920658</v>
+        <v>134859454</v>
       </c>
       <c r="B21" t="n">
         <v>101403</v>
@@ -2850,20 +2859,28 @@
           <t>Schreb.</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Stennässjön öster om, Upl</t>
+          <t>Aspbolsberget, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>624284</v>
+        <v>624157</v>
       </c>
       <c r="R21" t="n">
-        <v>6637664</v>
+        <v>6637639</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2887,27 +2904,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>13:16</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>13:16</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Rikligt på båda sidor djupt skogsdike.</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2916,25 +2918,26 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Annika Leers</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Annika Leers, Francis Rogers</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>134944920</v>
+        <v>134920658</v>
       </c>
       <c r="B22" t="n">
         <v>101403</v>
@@ -2962,32 +2965,20 @@
           <t>Schreb.</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Aspbolet, Upl</t>
+          <t>Stennässjön öster om, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>624233</v>
+        <v>624284</v>
       </c>
       <c r="R22" t="n">
-        <v>6637690</v>
+        <v>6637664</v>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3016,7 +3007,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3026,7 +3017,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:16</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Rikligt på båda sidor djupt skogsdike.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3035,29 +3031,28 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Ki Mähler</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Ki Mähler</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>134857234</v>
+        <v>134944920</v>
       </c>
       <c r="B23" t="n">
-        <v>99001</v>
+        <v>101403</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3065,37 +3060,49 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>223049</v>
+        <v>222498</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ormbär</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Paris quadrifolia</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Rödmossen, Upl</t>
+          <t>Aspbolet, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>624185</v>
+        <v>624233</v>
       </c>
       <c r="R23" t="n">
-        <v>6637624</v>
+        <v>6637690</v>
       </c>
       <c r="S23" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3119,22 +3126,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3143,6 +3150,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3161,7 +3169,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>134920885</v>
+        <v>134857234</v>
       </c>
       <c r="B24" t="n">
         <v>99001</v>
@@ -3190,27 +3198,19 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Stennässjön öster om, Upl</t>
+          <t>Rödmossen, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>624299</v>
+        <v>624185</v>
       </c>
       <c r="R24" t="n">
-        <v>6637654</v>
+        <v>6637624</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3234,27 +3234,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:26</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Frisk miljö intill skogsdike. Flera större klibbalsocklar, tussilago, hässlebrodd, stinksyska, blåsippa, hallon, skogsfräken...</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3263,22 +3258,142 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
+          <t>Ki Mähler</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Ki Mähler</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>134920885</v>
+      </c>
+      <c r="B25" t="n">
+        <v>99001</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Stennässjön öster om, Upl</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>624299</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6637654</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Skogs-Tibble</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Frisk miljö intill skogsdike. Flera större klibbalsocklar, tussilago, hässlebrodd, stinksyska, blåsippa, hallon, skogsfräken...</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
           <t>Anders Lindholm</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
+      <c r="AX25" t="inlineStr">
         <is>
           <t>Anders Lindholm</t>
         </is>
       </c>
-      <c r="AY24" t="inlineStr"/>
+      <c r="AY25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 23584-2026 artfynd.xlsx
+++ b/artfynd/A 23584-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1350,7 +1350,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134859622</v>
+        <v>134923574</v>
       </c>
       <c r="B8" t="n">
         <v>57162</v>
@@ -1379,8 +1379,16 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr">
         <is>
           <t>äldre spillning</t>
@@ -1389,17 +1397,17 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Aspbolsberget, Upl</t>
+          <t>Stennässjön öster om, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>623941</v>
+        <v>624255</v>
       </c>
       <c r="R8" t="n">
-        <v>6637639</v>
+        <v>6637537</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1423,12 +1431,27 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>15:26</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Minst 75 vintertuppkrokar under mattall.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1443,19 +1466,19 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Annika Leers</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Annika Leers, Ki Mähler, Francis Rogers</t>
+          <t>Anders Lindholm, Ki Mähler</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>134859734</v>
+        <v>134926712</v>
       </c>
       <c r="B9" t="n">
         <v>57162</v>
@@ -1485,7 +1508,11 @@
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr">
         <is>
           <t>äldre spillning</t>
@@ -1494,17 +1521,17 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Aspbolsberget, Upl</t>
+          <t>Stennässjön öster om, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>623935</v>
+        <v>623934</v>
       </c>
       <c r="R9" t="n">
-        <v>6637640</v>
+        <v>6637639</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1528,12 +1555,27 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>17:58</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Tiotalet vintertuppkrok, under mattall.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1548,19 +1590,19 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Annika Leers</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Annika Leers, Ki Mähler, Francis Rogers</t>
+          <t>Anders Lindholm, Ki Mähler</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134859868</v>
+        <v>135065035</v>
       </c>
       <c r="B10" t="n">
         <v>57162</v>
@@ -1589,27 +1631,24 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
           <t>äldre spillning</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Aspbolsberget, Upl</t>
+          <t>Aspbolsberget öst om, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>623941</v>
+        <v>624016</v>
       </c>
       <c r="R10" t="n">
-        <v>6637642</v>
+        <v>6637839</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1633,12 +1672,27 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Två krok på lavhäll. Foto miljöbild</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1653,19 +1707,19 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Annika Leers</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Annika Leers, Ki Mähler, Francis Rogers</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>134859936</v>
+        <v>135188692</v>
       </c>
       <c r="B11" t="n">
         <v>57162</v>
@@ -1708,13 +1762,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>623955</v>
+        <v>624017</v>
       </c>
       <c r="R11" t="n">
-        <v>6637675</v>
+        <v>6637855</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1738,12 +1792,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1758,22 +1822,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Annika Leers</t>
+          <t>Ki Mähler</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Annika Leers, Ki Mähler, Francis Rogers</t>
+          <t>Ki Mähler</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>134923574</v>
+        <v>134944921</v>
       </c>
       <c r="B12" t="n">
-        <v>57162</v>
+        <v>45268</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1781,53 +1845,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>102920</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Grön mosaikslända</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Aeshna viridis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Eversmann, 1836</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Stennässjön öster om, Upl</t>
+          <t>Aspbolet, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>624255</v>
+        <v>624306</v>
       </c>
       <c r="R12" t="n">
-        <v>6637537</v>
+        <v>6637654</v>
       </c>
       <c r="S12" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1856,7 +1904,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1866,12 +1914,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:26</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Minst 75 vintertuppkrokar under mattall.</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1886,22 +1929,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Ki Mähler</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anders Lindholm, Ki Mähler</t>
+          <t>Ki Mähler</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>134926712</v>
+        <v>134944923</v>
       </c>
       <c r="B13" t="n">
-        <v>57162</v>
+        <v>58839</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1909,16 +1952,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100138</v>
+        <v>208249</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1926,32 +1969,37 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Stennässjön öster om, Upl</t>
+          <t>Aspbolet, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>623934</v>
+        <v>624283</v>
       </c>
       <c r="R13" t="n">
-        <v>6637639</v>
+        <v>6637622</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>34</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1980,7 +2028,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1990,12 +2038,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:58</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Tiotalet vintertuppkrok, under mattall.</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2004,28 +2047,29 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Ki Mähler</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anders Lindholm, Ki Mähler</t>
+          <t>Ki Mähler</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135065035</v>
+        <v>134938793</v>
       </c>
       <c r="B14" t="n">
-        <v>57162</v>
+        <v>100815</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2033,42 +2077,41 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100138</v>
+        <v>219851</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Hässlebrodd</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Milium effusum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Aspbolsberget öst om, Upl</t>
+          <t>Stennässjön öster om, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>624016</v>
+        <v>624299</v>
       </c>
       <c r="R14" t="n">
-        <v>6637839</v>
+        <v>6637654</v>
       </c>
       <c r="S14" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2092,27 +2135,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:57</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Två krok på lavhäll. Foto miljöbild</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2121,6 +2159,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2139,10 +2178,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135188692</v>
+        <v>134920532</v>
       </c>
       <c r="B15" t="n">
-        <v>57162</v>
+        <v>108205</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2150,42 +2189,48 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100138</v>
+        <v>220083</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Brudborste</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Cirsium heterophyllum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
+          <t>(L.) Hill</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Aspbolsberget, Upl</t>
+          <t>Stennässjön öster om, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>624017</v>
+        <v>624238</v>
       </c>
       <c r="R15" t="n">
-        <v>6637855</v>
+        <v>6637712</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2212,22 +2257,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2242,22 +2287,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Ki Mähler</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Ki Mähler</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>134944921</v>
+        <v>134921287</v>
       </c>
       <c r="B16" t="n">
-        <v>45268</v>
+        <v>106141</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2265,37 +2310,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102920</v>
+        <v>221101</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grön mosaikslända</t>
+          <t>Springkorn</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Aeshna viridis</t>
+          <t>Impatiens noli-tangere</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Eversmann, 1836</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Aspbolet, Upl</t>
+          <t>Stennässjön öster om, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>624306</v>
+        <v>624299</v>
       </c>
       <c r="R16" t="n">
         <v>6637654</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2324,7 +2374,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2334,7 +2384,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2349,22 +2399,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Ki Mähler</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Ki Mähler</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>134944923</v>
+        <v>134859454</v>
       </c>
       <c r="B17" t="n">
-        <v>58839</v>
+        <v>101403</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2372,54 +2422,45 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>208249</v>
+        <v>222498</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Aspbolet, Upl</t>
+          <t>Aspbolsberget, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>624283</v>
+        <v>624157</v>
       </c>
       <c r="R17" t="n">
-        <v>6637622</v>
+        <v>6637639</v>
       </c>
       <c r="S17" t="n">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2443,22 +2484,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>14:06</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>14:06</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2474,22 +2505,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Ki Mähler</t>
+          <t>Annika Leers</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Ki Mähler</t>
+          <t>Annika Leers, Francis Rogers</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>134938793</v>
+        <v>134920658</v>
       </c>
       <c r="B18" t="n">
-        <v>100815</v>
+        <v>101403</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2497,41 +2528,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219851</v>
+        <v>222498</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hässlebrodd</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Milium effusum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Stennässjön öster om, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>624299</v>
+        <v>624284</v>
       </c>
       <c r="R18" t="n">
-        <v>6637654</v>
+        <v>6637664</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2560,7 +2587,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2570,7 +2597,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:16</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Rikligt på båda sidor djupt skogsdike.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2579,7 +2611,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2598,10 +2629,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>134920532</v>
+        <v>134944920</v>
       </c>
       <c r="B19" t="n">
-        <v>108205</v>
+        <v>101403</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2609,51 +2640,49 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220083</v>
+        <v>222498</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Brudborste</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cirsium heterophyllum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hill</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Stennässjön öster om, Upl</t>
+          <t>Aspbolet, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>624238</v>
+        <v>624233</v>
       </c>
       <c r="R19" t="n">
-        <v>6637712</v>
+        <v>6637690</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2682,7 +2711,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2692,7 +2721,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2701,28 +2730,29 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Ki Mähler</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Ki Mähler</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>134921287</v>
+        <v>134857234</v>
       </c>
       <c r="B20" t="n">
-        <v>106141</v>
+        <v>99001</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2730,16 +2760,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221101</v>
+        <v>223049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Springkorn</t>
+          <t>Ormbär</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Impatiens noli-tangere</t>
+          <t>Paris quadrifolia</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2748,24 +2778,19 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Stennässjön öster om, Upl</t>
+          <t>Rödmossen, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>624299</v>
+        <v>624185</v>
       </c>
       <c r="R20" t="n">
-        <v>6637654</v>
+        <v>6637624</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2789,7 +2814,7 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
@@ -2799,7 +2824,7 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -2819,22 +2844,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Ki Mähler</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Ki Mähler</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>134859454</v>
+        <v>134920885</v>
       </c>
       <c r="B21" t="n">
-        <v>101403</v>
+        <v>99001</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2842,45 +2867,45 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>222498</v>
+        <v>223049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ormbär</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Paris quadrifolia</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Aspbolsberget, Upl</t>
+          <t>Stennässjön öster om, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>624157</v>
+        <v>624299</v>
       </c>
       <c r="R21" t="n">
-        <v>6637639</v>
+        <v>6637654</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2904,12 +2929,27 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Frisk miljö intill skogsdike. Flera större klibbalsocklar, tussilago, hässlebrodd, stinksyska, blåsippa, hallon, skogsfräken...</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2925,475 +2965,15 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Annika Leers</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Annika Leers, Francis Rogers</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>134920658</v>
-      </c>
-      <c r="B22" t="n">
-        <v>101403</v>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
-        <v>222498</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Hepatica nobilis</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>Stennässjön öster om, Upl</t>
-        </is>
-      </c>
-      <c r="Q22" t="n">
-        <v>624284</v>
-      </c>
-      <c r="R22" t="n">
-        <v>6637664</v>
-      </c>
-      <c r="S22" t="n">
-        <v>10</v>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>Uppsala</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>Uppsala</t>
-        </is>
-      </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>Uppland</t>
-        </is>
-      </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>Skogs-Tibble</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>13:16</t>
-        </is>
-      </c>
-      <c r="AA22" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>13:16</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Rikligt på båda sidor djupt skogsdike.</t>
-        </is>
-      </c>
-      <c r="AD22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT22" t="inlineStr"/>
-      <c r="AW22" t="inlineStr">
-        <is>
-          <t>Anders Lindholm</t>
-        </is>
-      </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>Anders Lindholm</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>134944920</v>
-      </c>
-      <c r="B23" t="n">
-        <v>101403</v>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>222498</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Hepatica nobilis</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>Aspbolet, Upl</t>
-        </is>
-      </c>
-      <c r="Q23" t="n">
-        <v>624233</v>
-      </c>
-      <c r="R23" t="n">
-        <v>6637690</v>
-      </c>
-      <c r="S23" t="n">
-        <v>15</v>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>Uppsala</t>
-        </is>
-      </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>Uppsala</t>
-        </is>
-      </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>Uppland</t>
-        </is>
-      </c>
-      <c r="W23" t="inlineStr">
-        <is>
-          <t>Skogs-Tibble</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>13:11</t>
-        </is>
-      </c>
-      <c r="AA23" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>13:11</t>
-        </is>
-      </c>
-      <c r="AD23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF23" t="inlineStr"/>
-      <c r="AG23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT23" t="inlineStr"/>
-      <c r="AW23" t="inlineStr">
-        <is>
-          <t>Ki Mähler</t>
-        </is>
-      </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>Ki Mähler</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>134857234</v>
-      </c>
-      <c r="B24" t="n">
-        <v>99001</v>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E24" t="n">
-        <v>223049</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Ormbär</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Paris quadrifolia</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>Rödmossen, Upl</t>
-        </is>
-      </c>
-      <c r="Q24" t="n">
-        <v>624185</v>
-      </c>
-      <c r="R24" t="n">
-        <v>6637624</v>
-      </c>
-      <c r="S24" t="n">
-        <v>14</v>
-      </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>Uppsala</t>
-        </is>
-      </c>
-      <c r="U24" t="inlineStr">
-        <is>
-          <t>Uppsala</t>
-        </is>
-      </c>
-      <c r="V24" t="inlineStr">
-        <is>
-          <t>Uppland</t>
-        </is>
-      </c>
-      <c r="W24" t="inlineStr">
-        <is>
-          <t>Skogs-Tibble</t>
-        </is>
-      </c>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>2026-07-03</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>13:39</t>
-        </is>
-      </c>
-      <c r="AA24" t="inlineStr">
-        <is>
-          <t>2026-07-03</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>13:39</t>
-        </is>
-      </c>
-      <c r="AD24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT24" t="inlineStr"/>
-      <c r="AW24" t="inlineStr">
-        <is>
-          <t>Ki Mähler</t>
-        </is>
-      </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>Ki Mähler</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>134920885</v>
-      </c>
-      <c r="B25" t="n">
-        <v>99001</v>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E25" t="n">
-        <v>223049</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Ormbär</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Paris quadrifolia</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>Stennässjön öster om, Upl</t>
-        </is>
-      </c>
-      <c r="Q25" t="n">
-        <v>624299</v>
-      </c>
-      <c r="R25" t="n">
-        <v>6637654</v>
-      </c>
-      <c r="S25" t="n">
-        <v>5</v>
-      </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>Uppsala</t>
-        </is>
-      </c>
-      <c r="U25" t="inlineStr">
-        <is>
-          <t>Uppsala</t>
-        </is>
-      </c>
-      <c r="V25" t="inlineStr">
-        <is>
-          <t>Uppland</t>
-        </is>
-      </c>
-      <c r="W25" t="inlineStr">
-        <is>
-          <t>Skogs-Tibble</t>
-        </is>
-      </c>
-      <c r="Y25" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>13:26</t>
-        </is>
-      </c>
-      <c r="AA25" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>13:26</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Frisk miljö intill skogsdike. Flera större klibbalsocklar, tussilago, hässlebrodd, stinksyska, blåsippa, hallon, skogsfräken...</t>
-        </is>
-      </c>
-      <c r="AD25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF25" t="inlineStr"/>
-      <c r="AG25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT25" t="inlineStr"/>
-      <c r="AW25" t="inlineStr">
-        <is>
-          <t>Anders Lindholm</t>
-        </is>
-      </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>Anders Lindholm</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 23584-2026 artfynd.xlsx
+++ b/artfynd/A 23584-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ20"/>
+  <dimension ref="A1:AZ21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1769,10 +1769,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>134944921</v>
+        <v>135188692</v>
       </c>
       <c r="B11" t="n">
-        <v>45273</v>
+        <v>57167</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1780,37 +1780,45 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102920</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grön mosaikslända</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Aeshna viridis</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Eversmann, 1836</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Aspbolet, Upl</t>
+          <t>Aspbolsberget, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>624306</v>
+        <v>624017</v>
       </c>
       <c r="R11" t="n">
-        <v>6637654</v>
+        <v>6637855</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1834,22 +1842,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1875,16 +1883,16 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134944921</t>
+          <t>https://artportalen.se/Sighting/135188692</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>134944923</v>
+        <v>134944921</v>
       </c>
       <c r="B12" t="n">
-        <v>58844</v>
+        <v>45273</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1892,54 +1900,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>208249</v>
+        <v>102920</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Grön mosaikslända</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Aeshna viridis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>Eversmann, 1836</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Aspbolet, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>624283</v>
+        <v>624306</v>
       </c>
       <c r="R12" t="n">
-        <v>6637622</v>
+        <v>6637654</v>
       </c>
       <c r="S12" t="n">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1968,7 +1959,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1978,7 +1969,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1987,7 +1978,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2005,16 +1995,16 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134944923</t>
+          <t>https://artportalen.se/Sighting/134944921</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>134938793</v>
+        <v>134944923</v>
       </c>
       <c r="B13" t="n">
-        <v>100890</v>
+        <v>58844</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2022,41 +2012,54 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219851</v>
+        <v>208249</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Hässlebrodd</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Milium effusum</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Stennässjön öster om, Upl</t>
+          <t>Aspbolet, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>624299</v>
+        <v>624283</v>
       </c>
       <c r="R13" t="n">
-        <v>6637654</v>
+        <v>6637622</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>34</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2085,7 +2088,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2095,7 +2098,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2111,27 +2114,27 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Ki Mähler</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Ki Mähler</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134938793</t>
+          <t>https://artportalen.se/Sighting/134944923</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>134920532</v>
+        <v>134938793</v>
       </c>
       <c r="B14" t="n">
-        <v>108287</v>
+        <v>100890</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,51 +2142,41 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220083</v>
+        <v>219851</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Brudborste</t>
+          <t>Hässlebrodd</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cirsium heterophyllum</t>
+          <t>Milium effusum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hill</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Stennässjön öster om, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>624238</v>
+        <v>624299</v>
       </c>
       <c r="R14" t="n">
-        <v>6637712</v>
+        <v>6637654</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2212,7 +2205,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2222,7 +2215,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2231,6 +2224,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2248,16 +2242,16 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134920532</t>
+          <t>https://artportalen.se/Sighting/134938793</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>134921287</v>
+        <v>134920532</v>
       </c>
       <c r="B15" t="n">
-        <v>106223</v>
+        <v>108287</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2265,24 +2259,33 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221101</v>
+        <v>220083</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Springkorn</t>
+          <t>Brudborste</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Impatiens noli-tangere</t>
+          <t>Cirsium heterophyllum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) Hill</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -2294,13 +2297,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>624299</v>
+        <v>624238</v>
       </c>
       <c r="R15" t="n">
-        <v>6637654</v>
+        <v>6637712</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2329,7 +2332,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2339,7 +2342,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2365,16 +2368,16 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134921287</t>
+          <t>https://artportalen.se/Sighting/134920532</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>134859454</v>
+        <v>134921287</v>
       </c>
       <c r="B16" t="n">
-        <v>101403</v>
+        <v>106223</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2382,45 +2385,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222498</v>
+        <v>221101</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Springkorn</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Impatiens noli-tangere</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Aspbolsberget, Upl</t>
+          <t>Stennässjön öster om, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>624157</v>
+        <v>624299</v>
       </c>
       <c r="R16" t="n">
-        <v>6637639</v>
+        <v>6637654</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2444,12 +2444,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2458,34 +2468,33 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Annika Leers</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Annika Leers, Francis Rogers</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134859454</t>
+          <t>https://artportalen.se/Sighting/134921287</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>134920658</v>
+        <v>134859454</v>
       </c>
       <c r="B17" t="n">
-        <v>101478</v>
+        <v>101403</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2510,20 +2519,28 @@
           <t>Schreb.</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Stennässjön öster om, Upl</t>
+          <t>Aspbolsberget, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>624284</v>
+        <v>624157</v>
       </c>
       <c r="R17" t="n">
-        <v>6637664</v>
+        <v>6637639</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2547,27 +2564,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>13:16</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>13:16</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Rikligt på båda sidor djupt skogsdike.</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2576,30 +2578,31 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Annika Leers</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Annika Leers, Francis Rogers</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134920658</t>
+          <t>https://artportalen.se/Sighting/134859454</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>134944920</v>
+        <v>134920658</v>
       </c>
       <c r="B18" t="n">
         <v>101478</v>
@@ -2627,32 +2630,20 @@
           <t>Schreb.</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Aspbolet, Upl</t>
+          <t>Stennässjön öster om, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>624233</v>
+        <v>624284</v>
       </c>
       <c r="R18" t="n">
-        <v>6637690</v>
+        <v>6637664</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2681,7 +2672,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2691,7 +2682,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:16</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Rikligt på båda sidor djupt skogsdike.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2700,34 +2696,33 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Ki Mähler</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Ki Mähler</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134944920</t>
+          <t>https://artportalen.se/Sighting/134920658</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>134857234</v>
+        <v>134944920</v>
       </c>
       <c r="B19" t="n">
-        <v>99001</v>
+        <v>101478</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2735,37 +2730,49 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>223049</v>
+        <v>222498</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ormbär</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Paris quadrifolia</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Rödmossen, Upl</t>
+          <t>Aspbolet, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>624185</v>
+        <v>624233</v>
       </c>
       <c r="R19" t="n">
-        <v>6637624</v>
+        <v>6637690</v>
       </c>
       <c r="S19" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2789,22 +2796,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2813,6 +2820,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2830,16 +2838,16 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134857234</t>
+          <t>https://artportalen.se/Sighting/134944920</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>134920885</v>
+        <v>134857234</v>
       </c>
       <c r="B20" t="n">
-        <v>99075</v>
+        <v>99001</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2865,27 +2873,19 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Stennässjön öster om, Upl</t>
+          <t>Rödmossen, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>624299</v>
+        <v>624185</v>
       </c>
       <c r="R20" t="n">
-        <v>6637654</v>
+        <v>6637624</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2909,27 +2909,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:26</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Frisk miljö intill skogsdike. Flera större klibbalsocklar, tussilago, hässlebrodd, stinksyska, blåsippa, hallon, skogsfräken...</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2938,23 +2933,148 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Ki Mähler</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Ki Mähler</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134857234</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>134920885</v>
+      </c>
+      <c r="B21" t="n">
+        <v>99075</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Stennässjön öster om, Upl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>624299</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6637654</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Skogs-Tibble</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Frisk miljö intill skogsdike. Flera större klibbalsocklar, tussilago, hässlebrodd, stinksyska, blåsippa, hallon, skogsfräken...</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/134920885</t>
         </is>
@@ -2981,6 +3101,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
